--- a/AAII_Financials/Yearly/BRBR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRBR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>BRBR</t>
   </si>
@@ -970,14 +970,14 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>69000</v>
       </c>
       <c r="E14" s="3">
         <v>17400</v>
       </c>
       <c r="F14" s="3">
-        <v>7100</v>
+        <v>12100</v>
       </c>
       <c r="G14" s="3">
         <v>17600</v>
@@ -1077,13 +1077,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1959200</v>
+        <v>1890200</v>
       </c>
       <c r="E17" s="3">
         <v>1591100</v>
       </c>
       <c r="F17" s="3">
-        <v>1372400</v>
+        <v>1367400</v>
       </c>
       <c r="G17" s="3">
         <v>1159100</v>
@@ -1122,13 +1122,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>357400</v>
+        <v>426400</v>
       </c>
       <c r="E18" s="3">
         <v>405100</v>
       </c>
       <c r="F18" s="3">
-        <v>294400</v>
+        <v>299400</v>
       </c>
       <c r="G18" s="3">
         <v>212400</v>
@@ -1231,13 +1231,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>374400</v>
+        <v>443400</v>
       </c>
       <c r="E21" s="3">
         <v>422700</v>
       </c>
       <c r="F21" s="3">
-        <v>313900</v>
+        <v>318900</v>
       </c>
       <c r="G21" s="3">
         <v>232100</v>
